--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/57.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/57.xlsx
@@ -426,13 +426,13 @@
         <v>-17.83348809892964</v>
       </c>
       <c r="E2">
-        <v>-30.96591338672485</v>
+        <v>-27.08425264275508</v>
       </c>
       <c r="F2">
-        <v>-4.049928969537028</v>
+        <v>-2.227697125634912</v>
       </c>
       <c r="G2">
-        <v>-18.6230662294643</v>
+        <v>-19.24045317762852</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.51612972557038</v>
       </c>
       <c r="E3">
-        <v>-29.87472096865159</v>
+        <v>-28.04202942385136</v>
       </c>
       <c r="F3">
-        <v>-4.071115294231028</v>
+        <v>-2.217832098234973</v>
       </c>
       <c r="G3">
-        <v>-18.63619088725474</v>
+        <v>-18.74717196064049</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.18978062131027</v>
       </c>
       <c r="E4">
-        <v>-31.00675342956303</v>
+        <v>-27.85184257247722</v>
       </c>
       <c r="F4">
-        <v>-4.513970448176478</v>
+        <v>-2.173741414853566</v>
       </c>
       <c r="G4">
-        <v>-19.86575895072268</v>
+        <v>-18.68471355322383</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.86519668108394</v>
       </c>
       <c r="E5">
-        <v>-32.91324098679225</v>
+        <v>-29.69256310169305</v>
       </c>
       <c r="F5">
-        <v>-3.737284887637633</v>
+        <v>-1.928092375022984</v>
       </c>
       <c r="G5">
-        <v>-18.92511709392186</v>
+        <v>-17.63833452717147</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.55772766652758</v>
       </c>
       <c r="E6">
-        <v>-31.60677849981636</v>
+        <v>-29.02579058880366</v>
       </c>
       <c r="F6">
-        <v>-3.722677456856666</v>
+        <v>-1.780661201407533</v>
       </c>
       <c r="G6">
-        <v>-19.26874509980713</v>
+        <v>-18.25374673492151</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.27725108363364</v>
       </c>
       <c r="E7">
-        <v>-33.4946789354811</v>
+        <v>-29.36031802069829</v>
       </c>
       <c r="F7">
-        <v>-3.390815251212323</v>
+        <v>-1.633965618045769</v>
       </c>
       <c r="G7">
-        <v>-18.352313262535</v>
+        <v>-17.69255298674088</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.02639405975479</v>
       </c>
       <c r="E8">
-        <v>-32.76406173179457</v>
+        <v>-30.99897803969186</v>
       </c>
       <c r="F8">
-        <v>-3.183004377606816</v>
+        <v>-1.878026677565185</v>
       </c>
       <c r="G8">
-        <v>-18.30711107374179</v>
+        <v>-16.93292844948187</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.7961492015333</v>
       </c>
       <c r="E9">
-        <v>-32.98626036592893</v>
+        <v>-30.35104850714839</v>
       </c>
       <c r="F9">
-        <v>-3.069707739558525</v>
+        <v>-1.58742710898909</v>
       </c>
       <c r="G9">
-        <v>-18.32448316145912</v>
+        <v>-16.99430430850719</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.61060403923085</v>
       </c>
       <c r="E10">
-        <v>-33.4400700674226</v>
+        <v>-31.23899621904641</v>
       </c>
       <c r="F10">
-        <v>-3.491699632097066</v>
+        <v>-1.458855376033176</v>
       </c>
       <c r="G10">
-        <v>-19.58255005620188</v>
+        <v>-16.30272969008067</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.48165464236491</v>
       </c>
       <c r="E11">
-        <v>-34.58587135355436</v>
+        <v>-31.88390299518975</v>
       </c>
       <c r="F11">
-        <v>-3.186660791322773</v>
+        <v>-1.38824368188374</v>
       </c>
       <c r="G11">
-        <v>-19.2637478313156</v>
+        <v>-15.70504379842065</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.41755693301287</v>
       </c>
       <c r="E12">
-        <v>-35.49401832376359</v>
+        <v>-32.19916629865575</v>
       </c>
       <c r="F12">
-        <v>-2.956603282747684</v>
+        <v>-1.582215021290675</v>
       </c>
       <c r="G12">
-        <v>-17.74669695903566</v>
+        <v>-15.96723238403985</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.40775511245184</v>
       </c>
       <c r="E13">
-        <v>-35.30756067073477</v>
+        <v>-32.75490742158807</v>
       </c>
       <c r="F13">
-        <v>-2.689021559193179</v>
+        <v>-0.8610714951095378</v>
       </c>
       <c r="G13">
-        <v>-17.72526448721442</v>
+        <v>-15.15067970568753</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.47328843964278</v>
       </c>
       <c r="E14">
-        <v>-36.63222083051048</v>
+        <v>-33.1960056965422</v>
       </c>
       <c r="F14">
-        <v>-2.771309920252476</v>
+        <v>-1.184548137535342</v>
       </c>
       <c r="G14">
-        <v>-17.98350028145973</v>
+        <v>-15.36048883978438</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.61705995598084</v>
       </c>
       <c r="E15">
-        <v>-36.87249260440946</v>
+        <v>-33.78781611494561</v>
       </c>
       <c r="F15">
-        <v>-3.011899291986759</v>
+        <v>-0.8203522670575254</v>
       </c>
       <c r="G15">
-        <v>-16.77848322371102</v>
+        <v>-14.64751319971924</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.8334350514383</v>
       </c>
       <c r="E16">
-        <v>-36.15734919640714</v>
+        <v>-34.25629580798712</v>
       </c>
       <c r="F16">
-        <v>-1.997420928065483</v>
+        <v>-0.8210961409852393</v>
       </c>
       <c r="G16">
-        <v>-16.14091684521217</v>
+        <v>-14.85411938100685</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.09373119296818</v>
       </c>
       <c r="E17">
-        <v>-36.84019779202375</v>
+        <v>-34.12760789787415</v>
       </c>
       <c r="F17">
-        <v>-3.125159481869327</v>
+        <v>-0.3246928330206216</v>
       </c>
       <c r="G17">
-        <v>-15.6432276368386</v>
+        <v>-14.65224231402209</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.39341237938979</v>
       </c>
       <c r="E18">
-        <v>-40.76894108025128</v>
+        <v>-35.83567130950928</v>
       </c>
       <c r="F18">
-        <v>-2.015911745230774</v>
+        <v>-0.2458024350476078</v>
       </c>
       <c r="G18">
-        <v>-16.05273053313706</v>
+        <v>-14.28248251692258</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-16.71074368146478</v>
       </c>
       <c r="E19">
-        <v>-38.76971490381898</v>
+        <v>-35.94664382930425</v>
       </c>
       <c r="F19">
-        <v>-2.624046905219794</v>
+        <v>-0.2439377800239062</v>
       </c>
       <c r="G19">
-        <v>-15.45993266196578</v>
+        <v>-14.23243700000542</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.01601536781303</v>
       </c>
       <c r="E20">
-        <v>-37.89674059122733</v>
+        <v>-36.45850177486523</v>
       </c>
       <c r="F20">
-        <v>-1.572614243092229</v>
+        <v>0.2991605984365197</v>
       </c>
       <c r="G20">
-        <v>-15.16309756200534</v>
+        <v>-13.89665002122991</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.26396408728396</v>
       </c>
       <c r="E21">
-        <v>-40.48346607880774</v>
+        <v>-37.31842955384079</v>
       </c>
       <c r="F21">
-        <v>-1.862696082041574</v>
+        <v>0.4771577008478691</v>
       </c>
       <c r="G21">
-        <v>-16.35952706462517</v>
+        <v>-13.83418830326771</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.43938490421965</v>
       </c>
       <c r="E22">
-        <v>-42.24655497811008</v>
+        <v>-37.78432122398691</v>
       </c>
       <c r="F22">
-        <v>-2.164165487677204</v>
+        <v>0.2562089202339625</v>
       </c>
       <c r="G22">
-        <v>-14.6464472040556</v>
+        <v>-14.03202650469456</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.52542200470432</v>
       </c>
       <c r="E23">
-        <v>-41.08093256124674</v>
+        <v>-38.43624034213114</v>
       </c>
       <c r="F23">
-        <v>-2.475338389069227</v>
+        <v>-0.107793112271599</v>
       </c>
       <c r="G23">
-        <v>-15.51549520302414</v>
+        <v>-13.40170856565394</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-17.51013676962247</v>
       </c>
       <c r="E24">
-        <v>-41.75549404942932</v>
+        <v>-37.96896522317567</v>
       </c>
       <c r="F24">
-        <v>-1.670427866014795</v>
+        <v>0.3219754934444237</v>
       </c>
       <c r="G24">
-        <v>-15.67635792132286</v>
+        <v>-13.70777843239618</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-17.37801900379351</v>
       </c>
       <c r="E25">
-        <v>-40.70946863110855</v>
+        <v>-38.15499946388477</v>
       </c>
       <c r="F25">
-        <v>-1.195101538247008</v>
+        <v>0.5464829404207568</v>
       </c>
       <c r="G25">
-        <v>-15.80517786934698</v>
+        <v>-13.5467551526388</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-17.14671202268449</v>
       </c>
       <c r="E26">
-        <v>-40.66024638288218</v>
+        <v>-38.13883281167739</v>
       </c>
       <c r="F26">
-        <v>-1.575887951068093</v>
+        <v>0.1680606881672616</v>
       </c>
       <c r="G26">
-        <v>-13.79201029782463</v>
+        <v>-13.87496925849323</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-16.83611969957865</v>
       </c>
       <c r="E27">
-        <v>-41.24906121572951</v>
+        <v>-38.48699547880911</v>
       </c>
       <c r="F27">
-        <v>-2.754731803420249</v>
+        <v>0.5366932944544723</v>
       </c>
       <c r="G27">
-        <v>-14.3480230422363</v>
+        <v>-13.4089719025671</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-16.46820066648744</v>
       </c>
       <c r="E28">
-        <v>-40.95673916158638</v>
+        <v>-38.13220538996717</v>
       </c>
       <c r="F28">
-        <v>-2.454290401731494</v>
+        <v>0.4833066720788498</v>
       </c>
       <c r="G28">
-        <v>-13.57927298619829</v>
+        <v>-13.42413420113697</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-16.05636063482038</v>
       </c>
       <c r="E29">
-        <v>-40.06595209648556</v>
+        <v>-38.17285523689702</v>
       </c>
       <c r="F29">
-        <v>-1.544134143416579</v>
+        <v>0.06958934152687311</v>
       </c>
       <c r="G29">
-        <v>-14.91956390049993</v>
+        <v>-13.74444272424361</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-15.63928030382162</v>
       </c>
       <c r="E30">
-        <v>-39.67211524051248</v>
+        <v>-37.48229012157133</v>
       </c>
       <c r="F30">
-        <v>-1.803990512572576</v>
+        <v>0.2557839677563264</v>
       </c>
       <c r="G30">
-        <v>-15.12535237703933</v>
+        <v>-13.09369871922569</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-15.25116944307567</v>
       </c>
       <c r="E31">
-        <v>-39.06309435664291</v>
+        <v>-38.00690704264893</v>
       </c>
       <c r="F31">
-        <v>-1.691428636410568</v>
+        <v>0.3499096990016286</v>
       </c>
       <c r="G31">
-        <v>-14.04237195950478</v>
+        <v>-13.25663052848646</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-14.91775931986951</v>
       </c>
       <c r="E32">
-        <v>-40.65668020960113</v>
+        <v>-37.69444912883069</v>
       </c>
       <c r="F32">
-        <v>-1.069373590584904</v>
+        <v>0.4011674171520564</v>
       </c>
       <c r="G32">
-        <v>-16.35388920557179</v>
+        <v>-13.70150163805372</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-14.64581515035262</v>
       </c>
       <c r="E33">
-        <v>-41.62502644903132</v>
+        <v>-37.1687702805983</v>
       </c>
       <c r="F33">
-        <v>-2.290761564377441</v>
+        <v>0.5147862901200366</v>
       </c>
       <c r="G33">
-        <v>-15.64738402676316</v>
+        <v>-13.73584192693258</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-14.4565603192538</v>
       </c>
       <c r="E34">
-        <v>-39.64608783615339</v>
+        <v>-36.83742410169405</v>
       </c>
       <c r="F34">
-        <v>-1.870045357639211</v>
+        <v>0.4100284632598027</v>
       </c>
       <c r="G34">
-        <v>-16.00025838633961</v>
+        <v>-13.48180390443107</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-14.36044618871884</v>
       </c>
       <c r="E35">
-        <v>-37.95709835703857</v>
+        <v>-36.71126760855137</v>
       </c>
       <c r="F35">
-        <v>-1.111438087299063</v>
+        <v>0.06522136021191133</v>
       </c>
       <c r="G35">
-        <v>-15.20625548892804</v>
+        <v>-13.65976227989459</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-14.35292020799052</v>
       </c>
       <c r="E36">
-        <v>-37.53043006450987</v>
+        <v>-36.38096071443189</v>
       </c>
       <c r="F36">
-        <v>-1.972374411274437</v>
+        <v>-0.109495407284352</v>
       </c>
       <c r="G36">
-        <v>-15.28779588083306</v>
+        <v>-13.85428000414555</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-14.40982114377425</v>
       </c>
       <c r="E37">
-        <v>-37.9315532351613</v>
+        <v>-35.89750082937301</v>
       </c>
       <c r="F37">
-        <v>-1.948523228645631</v>
+        <v>-0.04134396432123108</v>
       </c>
       <c r="G37">
-        <v>-15.58383810513685</v>
+        <v>-13.65165144332338</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-14.52078372770014</v>
       </c>
       <c r="E38">
-        <v>-39.01040103308966</v>
+        <v>-35.35237444951467</v>
       </c>
       <c r="F38">
-        <v>-1.569205511229709</v>
+        <v>0.3858467620372796</v>
       </c>
       <c r="G38">
-        <v>-15.48227718908309</v>
+        <v>-13.98924597996333</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-14.6714347398961</v>
       </c>
       <c r="E39">
-        <v>-36.05550834444864</v>
+        <v>-35.06876744359929</v>
       </c>
       <c r="F39">
-        <v>-2.124125520895487</v>
+        <v>0.3303212950276287</v>
       </c>
       <c r="G39">
-        <v>-14.49713663441616</v>
+        <v>-14.27650367167866</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-14.83879836541961</v>
       </c>
       <c r="E40">
-        <v>-38.03063398221212</v>
+        <v>-35.29596551303813</v>
       </c>
       <c r="F40">
-        <v>-2.344814194144914</v>
+        <v>0.494696723867343</v>
       </c>
       <c r="G40">
-        <v>-16.91876593566487</v>
+        <v>-13.82752086455162</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-14.98959610485795</v>
       </c>
       <c r="E41">
-        <v>-37.21600000026129</v>
+        <v>-35.22111889463935</v>
       </c>
       <c r="F41">
-        <v>-2.092033739343631</v>
+        <v>0.5058796838051364</v>
       </c>
       <c r="G41">
-        <v>-15.62431945599106</v>
+        <v>-14.07582336690635</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-15.10874383448354</v>
       </c>
       <c r="E42">
-        <v>-37.74631827011455</v>
+        <v>-34.65411092837595</v>
       </c>
       <c r="F42">
-        <v>-1.90673623501141</v>
+        <v>0.445753464240337</v>
       </c>
       <c r="G42">
-        <v>-15.42115127624598</v>
+        <v>-13.67449751808989</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-15.18643732361097</v>
       </c>
       <c r="E43">
-        <v>-36.80676180418812</v>
+        <v>-33.9484546734197</v>
       </c>
       <c r="F43">
-        <v>-1.736945768459595</v>
+        <v>0.5949647994044036</v>
       </c>
       <c r="G43">
-        <v>-15.76088277003153</v>
+        <v>-13.77771039636775</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-15.21053723698044</v>
       </c>
       <c r="E44">
-        <v>-36.21329849277191</v>
+        <v>-33.69675982383638</v>
       </c>
       <c r="F44">
-        <v>-1.191897413132979</v>
+        <v>0.4068019722258986</v>
       </c>
       <c r="G44">
-        <v>-16.0524557578573</v>
+        <v>-14.42994911269665</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-15.16479742437196</v>
       </c>
       <c r="E45">
-        <v>-35.1002969438777</v>
+        <v>-32.54588211834201</v>
       </c>
       <c r="F45">
-        <v>-0.9875781081302727</v>
+        <v>0.6112645847892895</v>
       </c>
       <c r="G45">
-        <v>-15.35487912036808</v>
+        <v>-14.19852542677389</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-15.05135339032455</v>
       </c>
       <c r="E46">
-        <v>-35.16875162121465</v>
+        <v>-31.6110556435166</v>
       </c>
       <c r="F46">
-        <v>-1.246385764154325</v>
+        <v>0.3052159641509841</v>
       </c>
       <c r="G46">
-        <v>-17.34142493993639</v>
+        <v>-14.34776978550255</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.88104587228049</v>
       </c>
       <c r="E47">
-        <v>-32.8519888473645</v>
+        <v>-31.36534064386041</v>
       </c>
       <c r="F47">
-        <v>-1.035345086045304</v>
+        <v>0.4830283406315092</v>
       </c>
       <c r="G47">
-        <v>-15.94557479512193</v>
+        <v>-14.03312726108637</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.66215740611654</v>
       </c>
       <c r="E48">
-        <v>-34.09282695325824</v>
+        <v>-31.80304029907179</v>
       </c>
       <c r="F48">
-        <v>-0.9639812342941261</v>
+        <v>0.1457610376838989</v>
       </c>
       <c r="G48">
-        <v>-14.21917164402956</v>
+        <v>-14.34149961225117</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.3978644526715</v>
       </c>
       <c r="E49">
-        <v>-33.34493135699545</v>
+        <v>-30.92521146234391</v>
       </c>
       <c r="F49">
-        <v>-0.9559775484482772</v>
+        <v>-0.04069618101224187</v>
       </c>
       <c r="G49">
-        <v>-16.84354040937601</v>
+        <v>-13.65287800044568</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-14.10480836387236</v>
       </c>
       <c r="E50">
-        <v>-32.36296799622419</v>
+        <v>-31.35510176412906</v>
       </c>
       <c r="F50">
-        <v>-1.757293785341962</v>
+        <v>0.2614889340594066</v>
       </c>
       <c r="G50">
-        <v>-16.27246137221511</v>
+        <v>-13.86473967277688</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.80545933722716</v>
       </c>
       <c r="E51">
-        <v>-33.38314941338319</v>
+        <v>-30.71004328410646</v>
       </c>
       <c r="F51">
-        <v>-1.349616909891199</v>
+        <v>0.3988289359739534</v>
       </c>
       <c r="G51">
-        <v>-16.38432470598708</v>
+        <v>-14.97098660436143</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.51365769779075</v>
       </c>
       <c r="E52">
-        <v>-31.91142253173436</v>
+        <v>-29.9495902294204</v>
       </c>
       <c r="F52">
-        <v>-1.364650949884608</v>
+        <v>0.4620648467688621</v>
       </c>
       <c r="G52">
-        <v>-16.66048048323647</v>
+        <v>-14.46468501176745</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.23291987702792</v>
       </c>
       <c r="E53">
-        <v>-32.65020683829372</v>
+        <v>-30.12526785007396</v>
       </c>
       <c r="F53">
-        <v>-0.6820803518148291</v>
+        <v>0.212961514868606</v>
       </c>
       <c r="G53">
-        <v>-16.12209473854864</v>
+        <v>-14.30589138443077</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.97389376101735</v>
       </c>
       <c r="E54">
-        <v>-33.36595253333905</v>
+        <v>-29.73500848856694</v>
       </c>
       <c r="F54">
-        <v>-1.093501447926245</v>
+        <v>0.3617387855136056</v>
       </c>
       <c r="G54">
-        <v>-16.66942888782912</v>
+        <v>-14.25450178602466</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.75184411455916</v>
       </c>
       <c r="E55">
-        <v>-31.9357064736005</v>
+        <v>-29.94450248887278</v>
       </c>
       <c r="F55">
-        <v>-0.4989846480392487</v>
+        <v>0.2924085757363009</v>
       </c>
       <c r="G55">
-        <v>-15.31797977978737</v>
+        <v>-14.23770904377671</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.57102381198569</v>
       </c>
       <c r="E56">
-        <v>-30.05172090371539</v>
+        <v>-29.26783752451365</v>
       </c>
       <c r="F56">
-        <v>-1.113878457667711</v>
+        <v>0.3196237583878759</v>
       </c>
       <c r="G56">
-        <v>-16.55974223774922</v>
+        <v>-14.2206464920673</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.42576838632213</v>
       </c>
       <c r="E57">
-        <v>-29.77093287286979</v>
+        <v>-28.39750557650547</v>
       </c>
       <c r="F57">
-        <v>-1.146111890045445</v>
+        <v>0.2187418626053409</v>
       </c>
       <c r="G57">
-        <v>-16.26499443675128</v>
+        <v>-14.33422634370139</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.31583283373066</v>
       </c>
       <c r="E58">
-        <v>-30.5371438822566</v>
+        <v>-28.81563769552971</v>
       </c>
       <c r="F58">
-        <v>-1.62321009568782</v>
+        <v>0.2183906348265539</v>
       </c>
       <c r="G58">
-        <v>-15.89254647667389</v>
+        <v>-14.69577929840904</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.24828371336844</v>
       </c>
       <c r="E59">
-        <v>-29.0274615957125</v>
+        <v>-28.37152119264946</v>
       </c>
       <c r="F59">
-        <v>-0.7889115822842702</v>
+        <v>0.2794520811891139</v>
       </c>
       <c r="G59">
-        <v>-16.42711185180939</v>
+        <v>-14.52297047653186</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.21928889396891</v>
       </c>
       <c r="E60">
-        <v>-30.16296286771381</v>
+        <v>-27.47467502932637</v>
       </c>
       <c r="F60">
-        <v>-1.040556345376315</v>
+        <v>0.3225354698087162</v>
       </c>
       <c r="G60">
-        <v>-15.39745439127588</v>
+        <v>-14.50297147092912</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.21702862646026</v>
       </c>
       <c r="E61">
-        <v>-29.52421028774689</v>
+        <v>-28.18817686550091</v>
       </c>
       <c r="F61">
-        <v>-0.9035510038924993</v>
+        <v>0.4032109995347628</v>
       </c>
       <c r="G61">
-        <v>-16.3775529850865</v>
+        <v>-14.31029772054354</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.23387497885256</v>
       </c>
       <c r="E62">
-        <v>-30.15062504027992</v>
+        <v>-27.90973458419128</v>
       </c>
       <c r="F62">
-        <v>-1.388855017027006</v>
+        <v>0.1211013684699604</v>
       </c>
       <c r="G62">
-        <v>-15.66221692605186</v>
+        <v>-14.66152342844144</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.27259103011307</v>
       </c>
       <c r="E63">
-        <v>-29.16198444458435</v>
+        <v>-27.78025645536397</v>
       </c>
       <c r="F63">
-        <v>-1.307879618301146</v>
+        <v>0.1584027526180221</v>
       </c>
       <c r="G63">
-        <v>-16.22054374179549</v>
+        <v>-14.28999745529673</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.32666488571982</v>
       </c>
       <c r="E64">
-        <v>-29.60738250560877</v>
+        <v>-28.49906566307549</v>
       </c>
       <c r="F64">
-        <v>-0.7337572238710734</v>
+        <v>0.09297001147088917</v>
       </c>
       <c r="G64">
-        <v>-17.02724258135017</v>
+        <v>-14.10441158291072</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.38407630036287</v>
       </c>
       <c r="E65">
-        <v>-27.54431390261633</v>
+        <v>-27.65507584836994</v>
       </c>
       <c r="F65">
-        <v>-1.300382893305811</v>
+        <v>-0.1194101367284593</v>
       </c>
       <c r="G65">
-        <v>-16.71335651658971</v>
+        <v>-14.54643562331421</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.43618330793391</v>
       </c>
       <c r="E66">
-        <v>-30.97781648065402</v>
+        <v>-27.81588196038231</v>
       </c>
       <c r="F66">
-        <v>-1.498973209350756</v>
+        <v>0.08471947213900609</v>
       </c>
       <c r="G66">
-        <v>-17.4169964182341</v>
+        <v>-15.12904363531562</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.48736226535366</v>
       </c>
       <c r="E67">
-        <v>-30.7169152434131</v>
+        <v>-28.28064830473754</v>
       </c>
       <c r="F67">
-        <v>-1.564795283177205</v>
+        <v>0.253133192067368</v>
       </c>
       <c r="G67">
-        <v>-16.77618736037953</v>
+        <v>-15.05168115188116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.53292915435685</v>
       </c>
       <c r="E68">
-        <v>-29.13769371000721</v>
+        <v>-27.3984109985632</v>
       </c>
       <c r="F68">
-        <v>-1.388444146795218</v>
+        <v>-0.08164818030444103</v>
       </c>
       <c r="G68">
-        <v>-15.82975039361222</v>
+        <v>-15.31859719653044</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.56330935509179</v>
       </c>
       <c r="E69">
-        <v>-30.35746761905427</v>
+        <v>-28.12576090825319</v>
       </c>
       <c r="F69">
-        <v>-1.687363837565031</v>
+        <v>-0.01381648715880071</v>
       </c>
       <c r="G69">
-        <v>-16.34879427598685</v>
+        <v>-14.59071416990196</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.57050166666789</v>
       </c>
       <c r="E70">
-        <v>-29.11370185471457</v>
+        <v>-27.15591574392646</v>
       </c>
       <c r="F70">
-        <v>-1.843371098901664</v>
+        <v>0.1230662559494008</v>
       </c>
       <c r="G70">
-        <v>-16.05058529962762</v>
+        <v>-14.11189341582948</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.56044769881647</v>
       </c>
       <c r="E71">
-        <v>-28.49342318446194</v>
+        <v>-27.70549134949733</v>
       </c>
       <c r="F71">
-        <v>-2.051532371918555</v>
+        <v>-0.0257250969414464</v>
       </c>
       <c r="G71">
-        <v>-16.08053249457586</v>
+        <v>-14.24849976696196</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.52989109640238</v>
       </c>
       <c r="E72">
-        <v>-30.89263135609573</v>
+        <v>-27.44543014418484</v>
       </c>
       <c r="F72">
-        <v>-1.768572007531077</v>
+        <v>-0.2449848364210447</v>
       </c>
       <c r="G72">
-        <v>-16.52846585876695</v>
+        <v>-14.48398218171586</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.47145633944421</v>
       </c>
       <c r="E73">
-        <v>-29.59927200866103</v>
+        <v>-27.15060837238947</v>
       </c>
       <c r="F73">
-        <v>-1.736356799236205</v>
+        <v>-0.2731476713814223</v>
       </c>
       <c r="G73">
-        <v>-14.86097883136422</v>
+        <v>-14.75127728382939</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.37809575702853</v>
       </c>
       <c r="E74">
-        <v>-29.14018437071142</v>
+        <v>-27.39936197810481</v>
       </c>
       <c r="F74">
-        <v>-1.251792518192397</v>
+        <v>-0.440607940429162</v>
       </c>
       <c r="G74">
-        <v>-15.52059013260907</v>
+        <v>-14.5794550045229</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.25792087118755</v>
       </c>
       <c r="E75">
-        <v>-28.23309479918299</v>
+        <v>-27.42908688149116</v>
       </c>
       <c r="F75">
-        <v>-2.276655295875168</v>
+        <v>-0.3430370291556166</v>
       </c>
       <c r="G75">
-        <v>-16.68840990067853</v>
+        <v>-13.73727539315109</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.11041990281447</v>
       </c>
       <c r="E76">
-        <v>-29.37910665935611</v>
+        <v>-27.98431855109761</v>
       </c>
       <c r="F76">
-        <v>-2.314671561091846</v>
+        <v>-0.4096377683406969</v>
       </c>
       <c r="G76">
-        <v>-14.55746470577829</v>
+        <v>-13.99425318009147</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.93221790386622</v>
       </c>
       <c r="E77">
-        <v>-29.01968620584132</v>
+        <v>-27.8608044225384</v>
       </c>
       <c r="F77">
-        <v>-1.839332807813017</v>
+        <v>-0.3499580388060065</v>
       </c>
       <c r="G77">
-        <v>-14.17572238909939</v>
+        <v>-13.97073837512603</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.72001139425762</v>
       </c>
       <c r="E78">
-        <v>-30.21530749876847</v>
+        <v>-27.79737861558697</v>
       </c>
       <c r="F78">
-        <v>-1.894734848079651</v>
+        <v>-0.383549993724332</v>
       </c>
       <c r="G78">
-        <v>-15.81509791905541</v>
+        <v>-13.79842944562528</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.48667326900686</v>
       </c>
       <c r="E79">
-        <v>-29.64091585563557</v>
+        <v>-28.4908645966476</v>
       </c>
       <c r="F79">
-        <v>-2.331999350423606</v>
+        <v>-0.5029956030036039</v>
       </c>
       <c r="G79">
-        <v>-15.4385018454173</v>
+        <v>-13.88212003685805</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.23642214734289</v>
       </c>
       <c r="E80">
-        <v>-30.20320288774597</v>
+        <v>-29.82478775000601</v>
       </c>
       <c r="F80">
-        <v>-2.220573165970836</v>
+        <v>-0.5693834517661648</v>
       </c>
       <c r="G80">
-        <v>-13.48375050520816</v>
+        <v>-13.49373345528183</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.97106894357758</v>
       </c>
       <c r="E81">
-        <v>-32.08417249394197</v>
+        <v>-28.31978790558583</v>
       </c>
       <c r="F81">
-        <v>-1.99175075319332</v>
+        <v>-0.5239168501287083</v>
       </c>
       <c r="G81">
-        <v>-14.14853784440367</v>
+        <v>-13.99447829718815</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.69106101504889</v>
       </c>
       <c r="E82">
-        <v>-32.8405929425242</v>
+        <v>-29.51837987746201</v>
       </c>
       <c r="F82">
-        <v>-2.544355475968273</v>
+        <v>-0.8994232491243493</v>
       </c>
       <c r="G82">
-        <v>-14.76005685059953</v>
+        <v>-13.81298922490699</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.41330685078128</v>
       </c>
       <c r="E83">
-        <v>-33.58652997377867</v>
+        <v>-30.02984384578433</v>
       </c>
       <c r="F83">
-        <v>-2.243955492649658</v>
+        <v>-0.9227285376347106</v>
       </c>
       <c r="G83">
-        <v>-15.54549205615547</v>
+        <v>-13.65367584192064</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.14534171417515</v>
       </c>
       <c r="E84">
-        <v>-32.73999515668081</v>
+        <v>-30.6652544119336</v>
       </c>
       <c r="F84">
-        <v>-2.409610749126697</v>
+        <v>-1.04175913484518</v>
       </c>
       <c r="G84">
-        <v>-13.94380708716406</v>
+        <v>-13.08598183757365</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.892246485425622</v>
       </c>
       <c r="E85">
-        <v>-32.53665988102539</v>
+        <v>-31.81204290539904</v>
       </c>
       <c r="F85">
-        <v>-2.702155324364565</v>
+        <v>-1.052950378457001</v>
       </c>
       <c r="G85">
-        <v>-13.43500603268793</v>
+        <v>-12.95798621538881</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.655116085804099</v>
       </c>
       <c r="E86">
-        <v>-34.70499965503714</v>
+        <v>-32.57974378273437</v>
       </c>
       <c r="F86">
-        <v>-2.689135045527363</v>
+        <v>-0.8562893300931763</v>
       </c>
       <c r="G86">
-        <v>-14.27966027685035</v>
+        <v>-13.2214725348594</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.452800438485214</v>
       </c>
       <c r="E87">
-        <v>-35.80401501195866</v>
+        <v>-32.97980276199399</v>
       </c>
       <c r="F87">
-        <v>-2.768957356828526</v>
+        <v>-1.202252005667973</v>
       </c>
       <c r="G87">
-        <v>-12.79085994492978</v>
+        <v>-13.26032840785383</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.293403809785639</v>
       </c>
       <c r="E88">
-        <v>-35.6295781931832</v>
+        <v>-34.25874118395127</v>
       </c>
       <c r="F88">
-        <v>-3.677221623995446</v>
+        <v>-1.388635499665265</v>
       </c>
       <c r="G88">
-        <v>-13.55226390041615</v>
+        <v>-12.79136645839729</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.182011774474136</v>
       </c>
       <c r="E89">
-        <v>-35.52268582846914</v>
+        <v>-35.35172234925756</v>
       </c>
       <c r="F89">
-        <v>-4.107416010556508</v>
+        <v>-1.532220563429517</v>
       </c>
       <c r="G89">
-        <v>-14.73980955408135</v>
+        <v>-13.23730025308266</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.115453953198019</v>
       </c>
       <c r="E90">
-        <v>-36.63007206959384</v>
+        <v>-35.54201561977089</v>
       </c>
       <c r="F90">
-        <v>-3.298546719684097</v>
+        <v>-1.48579222723741</v>
       </c>
       <c r="G90">
-        <v>-13.56400640544394</v>
+        <v>-13.2062142304689</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.109865883954091</v>
       </c>
       <c r="E91">
-        <v>-37.66217469457803</v>
+        <v>-37.41569891128854</v>
       </c>
       <c r="F91">
-        <v>-3.336162883445223</v>
+        <v>-1.500651481708828</v>
       </c>
       <c r="G91">
-        <v>-13.85991786319893</v>
+        <v>-12.23065273931985</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.168732275296076</v>
       </c>
       <c r="E92">
-        <v>-39.16730133627042</v>
+        <v>-37.60025686947115</v>
       </c>
       <c r="F92">
-        <v>-3.901071347253957</v>
+        <v>-1.867644748905898</v>
       </c>
       <c r="G92">
-        <v>-13.13904326147709</v>
+        <v>-12.70284909176826</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.292117899388964</v>
       </c>
       <c r="E93">
-        <v>-40.03848237315503</v>
+        <v>-40.12385769362164</v>
       </c>
       <c r="F93">
-        <v>-3.958270944784665</v>
+        <v>-1.933458539058319</v>
       </c>
       <c r="G93">
-        <v>-13.4380384924019</v>
+        <v>-12.660593288505</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.46879462354145</v>
       </c>
       <c r="E94">
-        <v>-41.85593786715645</v>
+        <v>-41.23800041796578</v>
       </c>
       <c r="F94">
-        <v>-4.80854618028601</v>
+        <v>-2.266070417202196</v>
       </c>
       <c r="G94">
-        <v>-13.90744405496071</v>
+        <v>-13.31338652121173</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.706974192243164</v>
       </c>
       <c r="E95">
-        <v>-43.0259370541482</v>
+        <v>-42.72032392879255</v>
       </c>
       <c r="F95">
-        <v>-4.578783570506316</v>
+        <v>-2.272507660289351</v>
       </c>
       <c r="G95">
-        <v>-13.99953681077215</v>
+        <v>-12.95771806120013</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.00618131760329</v>
       </c>
       <c r="E96">
-        <v>-42.83266631197483</v>
+        <v>-44.29509397224891</v>
       </c>
       <c r="F96">
-        <v>-5.578186476064044</v>
+        <v>-2.65620081432686</v>
       </c>
       <c r="G96">
-        <v>-13.10590139008344</v>
+        <v>-13.27169020014461</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.35432017433203</v>
       </c>
       <c r="E97">
-        <v>-45.19813508801448</v>
+        <v>-45.53522790043445</v>
       </c>
       <c r="F97">
-        <v>-5.472727850381042</v>
+        <v>-2.593413050296866</v>
       </c>
       <c r="G97">
-        <v>-12.80253623904679</v>
+        <v>-13.80634992582798</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.74322309629521</v>
       </c>
       <c r="E98">
-        <v>-46.5906317884251</v>
+        <v>-47.6791297644638</v>
       </c>
       <c r="F98">
-        <v>-5.993810708377265</v>
+        <v>-2.885754675521047</v>
       </c>
       <c r="G98">
-        <v>-13.55303360225403</v>
+        <v>-12.98618213174678</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.16093328816287</v>
       </c>
       <c r="E99">
-        <v>-49.25501947311856</v>
+        <v>-49.02376728732436</v>
       </c>
       <c r="F99">
-        <v>-5.510848489890472</v>
+        <v>-2.985330235909368</v>
       </c>
       <c r="G99">
-        <v>-13.68806909952813</v>
+        <v>-13.57078805798114</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.62442898896762</v>
       </c>
       <c r="E100">
-        <v>-50.68436097017408</v>
+        <v>-50.4958621074863</v>
       </c>
       <c r="F100">
-        <v>-6.663584686808597</v>
+        <v>-3.224349023047943</v>
       </c>
       <c r="G100">
-        <v>-14.27605674803086</v>
+        <v>-14.08185021506059</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.08613341660529</v>
       </c>
       <c r="E101">
-        <v>-52.1397921381063</v>
+        <v>-52.75470343454134</v>
       </c>
       <c r="F101">
-        <v>-5.978516561019378</v>
+        <v>-3.534264462722516</v>
       </c>
       <c r="G101">
-        <v>-14.90728674236754</v>
+        <v>-13.97475737741071</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.59128502759901</v>
       </c>
       <c r="E102">
-        <v>-52.37921369101034</v>
+        <v>-54.13856546713784</v>
       </c>
       <c r="F102">
-        <v>-6.782619011672379</v>
+        <v>-3.687205936301389</v>
       </c>
       <c r="G102">
-        <v>-15.84866354027808</v>
+        <v>-13.5912654374143</v>
       </c>
     </row>
   </sheetData>
